--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/184.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/184.xlsx
@@ -426,13 +426,13 @@
         <v>-4.74464622778978</v>
       </c>
       <c r="E2">
-        <v>-8.347374442838433</v>
+        <v>-10.29704099973079</v>
       </c>
       <c r="F2">
-        <v>2.912957948268867</v>
+        <v>1.909510794305025</v>
       </c>
       <c r="G2">
-        <v>-10.66967754882486</v>
+        <v>-14.31088368710399</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.521643943697513</v>
       </c>
       <c r="E3">
-        <v>-9.275118384315851</v>
+        <v>-9.459916351620864</v>
       </c>
       <c r="F3">
-        <v>2.634296973917719</v>
+        <v>2.422812053381766</v>
       </c>
       <c r="G3">
-        <v>-11.67933103793732</v>
+        <v>-12.87792067152153</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.211416671328553</v>
       </c>
       <c r="E4">
-        <v>-9.118917730369278</v>
+        <v>-11.03287274123715</v>
       </c>
       <c r="F4">
-        <v>2.679111100206909</v>
+        <v>2.766243432262557</v>
       </c>
       <c r="G4">
-        <v>-10.67857960577996</v>
+        <v>-13.57223807692734</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.85689338895527</v>
       </c>
       <c r="E5">
-        <v>-10.54168727952117</v>
+        <v>-11.8672938903645</v>
       </c>
       <c r="F5">
-        <v>3.000524215745345</v>
+        <v>2.717607823599411</v>
       </c>
       <c r="G5">
-        <v>-10.75753611689157</v>
+        <v>-12.7265492872839</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.468468569643879</v>
       </c>
       <c r="E6">
-        <v>-11.05690988126986</v>
+        <v>-12.56786240477312</v>
       </c>
       <c r="F6">
-        <v>3.068531715166146</v>
+        <v>2.675135998359156</v>
       </c>
       <c r="G6">
-        <v>-10.59424676871256</v>
+        <v>-12.42590871522606</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.073723413294076</v>
       </c>
       <c r="E7">
-        <v>-11.38719866149331</v>
+        <v>-13.45672486842068</v>
       </c>
       <c r="F7">
-        <v>3.493517613868406</v>
+        <v>2.791044266898338</v>
       </c>
       <c r="G7">
-        <v>-10.01864552634502</v>
+        <v>-11.24408037370718</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.683804242424871</v>
       </c>
       <c r="E8">
-        <v>-12.48474679283634</v>
+        <v>-14.53024491667902</v>
       </c>
       <c r="F8">
-        <v>3.36460236864572</v>
+        <v>2.939388416291636</v>
       </c>
       <c r="G8">
-        <v>-9.585530163987711</v>
+        <v>-11.75024623393405</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.315692892659245</v>
       </c>
       <c r="E9">
-        <v>-12.82675526379164</v>
+        <v>-14.09739978560386</v>
       </c>
       <c r="F9">
-        <v>3.789402973755874</v>
+        <v>2.930811065053616</v>
       </c>
       <c r="G9">
-        <v>-8.909003630309947</v>
+        <v>-10.80217882348865</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.97185061905072</v>
       </c>
       <c r="E10">
-        <v>-12.9383776196067</v>
+        <v>-13.64333875380277</v>
       </c>
       <c r="F10">
-        <v>3.983413283220868</v>
+        <v>3.570859475954807</v>
       </c>
       <c r="G10">
-        <v>-7.811875596413318</v>
+        <v>-10.73705708218564</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.653724435438045</v>
       </c>
       <c r="E11">
-        <v>-14.74824565540827</v>
+        <v>-15.75590810617305</v>
       </c>
       <c r="F11">
-        <v>3.925446479303953</v>
+        <v>3.526702587620524</v>
       </c>
       <c r="G11">
-        <v>-7.180634015167246</v>
+        <v>-8.410812874287183</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.360949046194083</v>
       </c>
       <c r="E12">
-        <v>-14.75574933683898</v>
+        <v>-16.27793700435527</v>
       </c>
       <c r="F12">
-        <v>4.351235316905341</v>
+        <v>3.792738258413789</v>
       </c>
       <c r="G12">
-        <v>-7.016374677145227</v>
+        <v>-9.853300329386121</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.087655013328131</v>
       </c>
       <c r="E13">
-        <v>-15.76492882639633</v>
+        <v>-17.72184999864898</v>
       </c>
       <c r="F13">
-        <v>4.544544044649795</v>
+        <v>3.748389741663738</v>
       </c>
       <c r="G13">
-        <v>-6.4544228140361</v>
+        <v>-8.303451882448618</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.8338907363330752</v>
       </c>
       <c r="E14">
-        <v>-17.4991713462698</v>
+        <v>-18.48559525393862</v>
       </c>
       <c r="F14">
-        <v>4.775359679589602</v>
+        <v>4.494608213430074</v>
       </c>
       <c r="G14">
-        <v>-6.757000055234408</v>
+        <v>-7.601493737938173</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.5915074826531019</v>
       </c>
       <c r="E15">
-        <v>-17.56885550429984</v>
+        <v>-19.92458126851198</v>
       </c>
       <c r="F15">
-        <v>5.153385530487252</v>
+        <v>4.363111527565222</v>
       </c>
       <c r="G15">
-        <v>-5.751928361148294</v>
+        <v>-6.925357848634044</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.3539020708197957</v>
       </c>
       <c r="E16">
-        <v>-18.24784584006191</v>
+        <v>-19.67827303876078</v>
       </c>
       <c r="F16">
-        <v>4.82115411984045</v>
+        <v>4.582245747672747</v>
       </c>
       <c r="G16">
-        <v>-4.708725803540854</v>
+        <v>-6.545595238187628</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.1143127289486079</v>
       </c>
       <c r="E17">
-        <v>-19.14769438165208</v>
+        <v>-20.5513492420176</v>
       </c>
       <c r="F17">
-        <v>5.119527481721073</v>
+        <v>4.774279592155272</v>
       </c>
       <c r="G17">
-        <v>-4.864225438065961</v>
+        <v>-7.320901829666166</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.1341008020088024</v>
       </c>
       <c r="E18">
-        <v>-20.54745475437101</v>
+        <v>-21.24077318189335</v>
       </c>
       <c r="F18">
-        <v>5.33967844102631</v>
+        <v>4.851179600291266</v>
       </c>
       <c r="G18">
-        <v>-3.974443492384965</v>
+        <v>-6.420486411713031</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.3897878153007955</v>
       </c>
       <c r="E19">
-        <v>-21.70451156264884</v>
+        <v>-21.96167454459642</v>
       </c>
       <c r="F19">
-        <v>5.669906463690081</v>
+        <v>4.974485359161466</v>
       </c>
       <c r="G19">
-        <v>-4.354732479572125</v>
+        <v>-5.543254744171413</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.6482514230715062</v>
       </c>
       <c r="E20">
-        <v>-21.11383099851034</v>
+        <v>-23.06154125463138</v>
       </c>
       <c r="F20">
-        <v>5.992955547439166</v>
+        <v>5.232398202314442</v>
       </c>
       <c r="G20">
-        <v>-3.981498264929152</v>
+        <v>-5.607598507272687</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.8936516806171507</v>
       </c>
       <c r="E21">
-        <v>-22.12108588661443</v>
+        <v>-22.09910014530719</v>
       </c>
       <c r="F21">
-        <v>5.801312878317754</v>
+        <v>5.584318244901987</v>
       </c>
       <c r="G21">
-        <v>-3.832086723650765</v>
+        <v>-4.780468635922399</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.106155019124966</v>
       </c>
       <c r="E22">
-        <v>-23.28623507794397</v>
+        <v>-23.68834092745506</v>
       </c>
       <c r="F22">
-        <v>5.962477127096534</v>
+        <v>5.680312995260434</v>
       </c>
       <c r="G22">
-        <v>-4.025243813685081</v>
+        <v>-5.537871797124557</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.260038257085549</v>
       </c>
       <c r="E23">
-        <v>-23.72079197219403</v>
+        <v>-24.28972680414769</v>
       </c>
       <c r="F23">
-        <v>6.10796743843021</v>
+        <v>5.293491241708433</v>
       </c>
       <c r="G23">
-        <v>-3.093576845841226</v>
+        <v>-4.950001672988477</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.331784619644719</v>
       </c>
       <c r="E24">
-        <v>-24.50873286410664</v>
+        <v>-24.44890719399131</v>
       </c>
       <c r="F24">
-        <v>5.793698420276321</v>
+        <v>5.2209670130168</v>
       </c>
       <c r="G24">
-        <v>-3.251211782239163</v>
+        <v>-5.506597073415063</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.302650348525514</v>
       </c>
       <c r="E25">
-        <v>-22.16498038517078</v>
+        <v>-25.57900146802747</v>
       </c>
       <c r="F25">
-        <v>5.809522809783393</v>
+        <v>5.310528749946731</v>
       </c>
       <c r="G25">
-        <v>-3.933204026602263</v>
+        <v>-6.895516591143053</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.160382887864316</v>
       </c>
       <c r="E26">
-        <v>-24.00327365231849</v>
+        <v>-25.14775035980302</v>
       </c>
       <c r="F26">
-        <v>5.5784727863681</v>
+        <v>5.468666536721106</v>
       </c>
       <c r="G26">
-        <v>-3.336474882603093</v>
+        <v>-6.491563824441184</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.9053609609788585</v>
       </c>
       <c r="E27">
-        <v>-24.35812487555954</v>
+        <v>-25.356146205162</v>
       </c>
       <c r="F27">
-        <v>5.837006442239929</v>
+        <v>5.024842456154694</v>
       </c>
       <c r="G27">
-        <v>-3.574959962161111</v>
+        <v>-5.83770459607081</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.5438383539735598</v>
       </c>
       <c r="E28">
-        <v>-24.71267721951608</v>
+        <v>-24.93670988562355</v>
       </c>
       <c r="F28">
-        <v>5.590412345264599</v>
+        <v>5.323608577102346</v>
       </c>
       <c r="G28">
-        <v>-2.792049047578868</v>
+        <v>-6.337057353577858</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.09664856098842757</v>
       </c>
       <c r="E29">
-        <v>-23.34892727210616</v>
+        <v>-24.36107744061254</v>
       </c>
       <c r="F29">
-        <v>5.550064269656947</v>
+        <v>5.217221548526785</v>
       </c>
       <c r="G29">
-        <v>-3.737017787399514</v>
+        <v>-5.763472233443732</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.4122899146252099</v>
       </c>
       <c r="E30">
-        <v>-22.34667634778054</v>
+        <v>-25.2613335448634</v>
       </c>
       <c r="F30">
-        <v>5.327507661066157</v>
+        <v>5.446150989721303</v>
       </c>
       <c r="G30">
-        <v>-3.42710768783172</v>
+        <v>-5.899985889301119</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.9511202262946175</v>
       </c>
       <c r="E31">
-        <v>-23.35879028849486</v>
+        <v>-24.43979137581387</v>
       </c>
       <c r="F31">
-        <v>5.614384901706606</v>
+        <v>4.912963135464389</v>
       </c>
       <c r="G31">
-        <v>-3.366584294282764</v>
+        <v>-6.138934445234635</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.487339177506115</v>
       </c>
       <c r="E32">
-        <v>-21.99871746197916</v>
+        <v>-25.00344147860058</v>
       </c>
       <c r="F32">
-        <v>5.705970614796469</v>
+        <v>5.002371252920524</v>
       </c>
       <c r="G32">
-        <v>-3.858293002139635</v>
+        <v>-6.752044168562119</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.99192253538899</v>
       </c>
       <c r="E33">
-        <v>-21.58295373486094</v>
+        <v>-22.51551597268252</v>
       </c>
       <c r="F33">
-        <v>5.447109131800144</v>
+        <v>4.870477056870896</v>
       </c>
       <c r="G33">
-        <v>-4.61966219689784</v>
+        <v>-5.703534806455227</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.437524981041693</v>
       </c>
       <c r="E34">
-        <v>-22.26738729638024</v>
+        <v>-22.98109744235913</v>
       </c>
       <c r="F34">
-        <v>5.582683860397254</v>
+        <v>5.109154207974944</v>
       </c>
       <c r="G34">
-        <v>-5.168103723661202</v>
+        <v>-6.799759061419635</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.808325052731458</v>
       </c>
       <c r="E35">
-        <v>-21.32978939546213</v>
+        <v>-20.8956627062428</v>
       </c>
       <c r="F35">
-        <v>5.831518901242931</v>
+        <v>4.882280417058666</v>
       </c>
       <c r="G35">
-        <v>-3.828799351930268</v>
+        <v>-7.138186200262711</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.092367775657666</v>
       </c>
       <c r="E36">
-        <v>-21.57003399851706</v>
+        <v>-22.65944446206831</v>
       </c>
       <c r="F36">
-        <v>5.640066276831371</v>
+        <v>4.688151329650013</v>
       </c>
       <c r="G36">
-        <v>-5.170037082256136</v>
+        <v>-6.721074015042237</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.289256143405158</v>
       </c>
       <c r="E37">
-        <v>-19.57161389045812</v>
+        <v>-20.97294564365771</v>
       </c>
       <c r="F37">
-        <v>5.330409010303242</v>
+        <v>5.22269958728829</v>
       </c>
       <c r="G37">
-        <v>-4.549524979102841</v>
+        <v>-6.777492332122497</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.404335168800424</v>
       </c>
       <c r="E38">
-        <v>-19.40451319957509</v>
+        <v>-21.33291404252742</v>
       </c>
       <c r="F38">
-        <v>5.614253454115624</v>
+        <v>4.985241889739131</v>
       </c>
       <c r="G38">
-        <v>-5.060769216186952</v>
+        <v>-7.7868875986829</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.447666148633498</v>
       </c>
       <c r="E39">
-        <v>-18.31959498223944</v>
+        <v>-21.54577496325797</v>
       </c>
       <c r="F39">
-        <v>5.559020126608758</v>
+        <v>4.983362030817504</v>
       </c>
       <c r="G39">
-        <v>-5.621453140354538</v>
+        <v>-6.982583938825886</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.436734864539255</v>
       </c>
       <c r="E40">
-        <v>-18.2006047992139</v>
+        <v>-19.61055423845008</v>
       </c>
       <c r="F40">
-        <v>5.599574083985416</v>
+        <v>5.095128908387812</v>
       </c>
       <c r="G40">
-        <v>-6.249917173893162</v>
+        <v>-7.090547449952598</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.386676999410218</v>
       </c>
       <c r="E41">
-        <v>-18.7582275030964</v>
+        <v>-20.08829466083728</v>
       </c>
       <c r="F41">
-        <v>5.833826360761726</v>
+        <v>4.673386439400372</v>
       </c>
       <c r="G41">
-        <v>-5.329506060882829</v>
+        <v>-7.306477782751561</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.316654546517219</v>
       </c>
       <c r="E42">
-        <v>-18.07747106247133</v>
+        <v>-18.03787861422227</v>
       </c>
       <c r="F42">
-        <v>5.801437991085074</v>
+        <v>5.1458819318599</v>
       </c>
       <c r="G42">
-        <v>-4.910712118528406</v>
+        <v>-7.057683664384253</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.243431998728104</v>
       </c>
       <c r="E43">
-        <v>-17.01031352019377</v>
+        <v>-18.5038902889296</v>
       </c>
       <c r="F43">
-        <v>5.702304335602226</v>
+        <v>5.149787350647373</v>
       </c>
       <c r="G43">
-        <v>-5.296248320395311</v>
+        <v>-7.522573642827488</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.178429005324268</v>
       </c>
       <c r="E44">
-        <v>-16.96251547704281</v>
+        <v>-17.86239118947703</v>
       </c>
       <c r="F44">
-        <v>5.945138714734303</v>
+        <v>5.195664143605824</v>
       </c>
       <c r="G44">
-        <v>-5.622085454552538</v>
+        <v>-7.92878751213268</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.134873686029688</v>
       </c>
       <c r="E45">
-        <v>-15.93775350842506</v>
+        <v>-17.29909430766291</v>
       </c>
       <c r="F45">
-        <v>5.60427769055427</v>
+        <v>5.300149141376941</v>
       </c>
       <c r="G45">
-        <v>-5.381617358216497</v>
+        <v>-6.992273905619332</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.114630300934136</v>
       </c>
       <c r="E46">
-        <v>-14.80224770794974</v>
+        <v>-15.96869657131948</v>
       </c>
       <c r="F46">
-        <v>5.737239304390905</v>
+        <v>5.133345315833282</v>
       </c>
       <c r="G46">
-        <v>-6.311761475112287</v>
+        <v>-6.932753607368776</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.122183515550676</v>
       </c>
       <c r="E47">
-        <v>-14.91917290682779</v>
+        <v>-18.04735218184632</v>
       </c>
       <c r="F47">
-        <v>5.774554583170489</v>
+        <v>4.941408077411597</v>
       </c>
       <c r="G47">
-        <v>-6.130942788302834</v>
+        <v>-8.062381266824429</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.155628210553628</v>
       </c>
       <c r="E48">
-        <v>-13.25064760175363</v>
+        <v>-15.68244267234662</v>
       </c>
       <c r="F48">
-        <v>5.913564369898187</v>
+        <v>4.799820017453564</v>
       </c>
       <c r="G48">
-        <v>-5.933568063251486</v>
+        <v>-7.510771547979986</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.208969560158695</v>
       </c>
       <c r="E49">
-        <v>-12.87376988093927</v>
+        <v>-15.45995421587577</v>
       </c>
       <c r="F49">
-        <v>5.519877251202757</v>
+        <v>5.086081196492906</v>
       </c>
       <c r="G49">
-        <v>-6.321928160463389</v>
+        <v>-7.390095541982473</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.281412533111985</v>
       </c>
       <c r="E50">
-        <v>-12.85856779369552</v>
+        <v>-14.8535281476126</v>
       </c>
       <c r="F50">
-        <v>6.193283259800848</v>
+        <v>4.872584969444345</v>
       </c>
       <c r="G50">
-        <v>-5.218884181688082</v>
+        <v>-7.254889551613098</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.363517885527195</v>
       </c>
       <c r="E51">
-        <v>-12.56396338865252</v>
+        <v>-14.78581840424991</v>
       </c>
       <c r="F51">
-        <v>5.717408138917772</v>
+        <v>5.070299567045552</v>
       </c>
       <c r="G51">
-        <v>-5.630484308585669</v>
+        <v>-8.49790008524325</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.455495200610132</v>
       </c>
       <c r="E52">
-        <v>-11.002676876554</v>
+        <v>-14.9853610829239</v>
       </c>
       <c r="F52">
-        <v>5.747843799200687</v>
+        <v>4.861199707618251</v>
       </c>
       <c r="G52">
-        <v>-5.09039528821789</v>
+        <v>-7.586510208827432</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.551587335146477</v>
       </c>
       <c r="E53">
-        <v>-11.31432645776188</v>
+        <v>-13.78954506561442</v>
       </c>
       <c r="F53">
-        <v>5.772137847943529</v>
+        <v>4.878172283914016</v>
       </c>
       <c r="G53">
-        <v>-5.637489422946767</v>
+        <v>-6.848000331017895</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.651707794182036</v>
       </c>
       <c r="E54">
-        <v>-9.657946519976289</v>
+        <v>-13.5573339754491</v>
       </c>
       <c r="F54">
-        <v>5.941904787254976</v>
+        <v>5.071875354431414</v>
       </c>
       <c r="G54">
-        <v>-6.444269370867155</v>
+        <v>-7.963832947211405</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.758950321334499</v>
       </c>
       <c r="E55">
-        <v>-10.98694495785135</v>
+        <v>-13.86550116014507</v>
       </c>
       <c r="F55">
-        <v>5.508959182621717</v>
+        <v>4.662359095111166</v>
       </c>
       <c r="G55">
-        <v>-6.20958810813376</v>
+        <v>-7.178061721283232</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.871813203798259</v>
       </c>
       <c r="E56">
-        <v>-9.397989469565971</v>
+        <v>-12.86873421784274</v>
       </c>
       <c r="F56">
-        <v>6.002690587701372</v>
+        <v>5.036715499402743</v>
       </c>
       <c r="G56">
-        <v>-5.480006771643636</v>
+        <v>-6.818692071358726</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.996927426150156</v>
       </c>
       <c r="E57">
-        <v>-9.295935779329112</v>
+        <v>-11.98588103920336</v>
       </c>
       <c r="F57">
-        <v>5.500883866158891</v>
+        <v>4.891743059903416</v>
       </c>
       <c r="G57">
-        <v>-5.999348603116804</v>
+        <v>-7.012531133774133</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.130042183723471</v>
       </c>
       <c r="E58">
-        <v>-10.41998001209103</v>
+        <v>-11.31108859884639</v>
       </c>
       <c r="F58">
-        <v>5.559292524026214</v>
+        <v>4.899758195541455</v>
       </c>
       <c r="G58">
-        <v>-5.713876950719911</v>
+        <v>-7.828527640475852</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.274711019508495</v>
       </c>
       <c r="E59">
-        <v>-9.659581299093057</v>
+        <v>-10.74108957550092</v>
       </c>
       <c r="F59">
-        <v>5.713901814020989</v>
+        <v>4.94229970384199</v>
       </c>
       <c r="G59">
-        <v>-5.890166811231641</v>
+        <v>-7.596892079638587</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.428124471696004</v>
       </c>
       <c r="E60">
-        <v>-8.592124877530994</v>
+        <v>-10.24163964872095</v>
       </c>
       <c r="F60">
-        <v>5.416361481451887</v>
+        <v>4.546861006404083</v>
       </c>
       <c r="G60">
-        <v>-6.344545807587689</v>
+        <v>-6.324781850718241</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.584279189115431</v>
       </c>
       <c r="E61">
-        <v>-7.838623030446707</v>
+        <v>-10.78212660695843</v>
       </c>
       <c r="F61">
-        <v>5.654816913727775</v>
+        <v>4.770795439141306</v>
       </c>
       <c r="G61">
-        <v>-6.298459703135495</v>
+        <v>-8.432367836293377</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.741995062590751</v>
       </c>
       <c r="E62">
-        <v>-7.476222841034871</v>
+        <v>-10.70747924141599</v>
       </c>
       <c r="F62">
-        <v>5.564175089363513</v>
+        <v>4.664574699686867</v>
       </c>
       <c r="G62">
-        <v>-6.096976591069912</v>
+        <v>-6.811895521366603</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.889690529508448</v>
       </c>
       <c r="E63">
-        <v>-7.280515779845381</v>
+        <v>-10.50587610706852</v>
       </c>
       <c r="F63">
-        <v>5.56091899000137</v>
+        <v>5.035172969841105</v>
       </c>
       <c r="G63">
-        <v>-6.082198315782605</v>
+        <v>-7.424667569049082</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.024247379656169</v>
       </c>
       <c r="E64">
-        <v>-7.493666522912418</v>
+        <v>-8.584231747335624</v>
       </c>
       <c r="F64">
-        <v>5.340345181216709</v>
+        <v>4.29510402814442</v>
       </c>
       <c r="G64">
-        <v>-6.511638972591324</v>
+        <v>-6.923798581685047</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.134976671706556</v>
       </c>
       <c r="E65">
-        <v>-7.097592600779545</v>
+        <v>-9.284193446227222</v>
       </c>
       <c r="F65">
-        <v>5.239304743811673</v>
+        <v>4.654438981828054</v>
       </c>
       <c r="G65">
-        <v>-6.96403164162381</v>
+        <v>-8.234877242148155</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.214184472538761</v>
       </c>
       <c r="E66">
-        <v>-7.790435538531087</v>
+        <v>-9.720059069465496</v>
       </c>
       <c r="F66">
-        <v>5.356502148966023</v>
+        <v>4.190858169966535</v>
       </c>
       <c r="G66">
-        <v>-6.374410238897455</v>
+        <v>-7.894241969430386</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.257536911009259</v>
       </c>
       <c r="E67">
-        <v>-6.474886668458802</v>
+        <v>-9.181465013363221</v>
       </c>
       <c r="F67">
-        <v>5.257788175550766</v>
+        <v>4.076063246685906</v>
       </c>
       <c r="G67">
-        <v>-6.457726738484292</v>
+        <v>-8.193952278191684</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.258822852793881</v>
       </c>
       <c r="E68">
-        <v>-5.539027701559638</v>
+        <v>-8.955833795931046</v>
       </c>
       <c r="F68">
-        <v>5.314521272559554</v>
+        <v>4.43361653121467</v>
       </c>
       <c r="G68">
-        <v>-6.579174101592456</v>
+        <v>-7.760697872921726</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.219317673639472</v>
       </c>
       <c r="E69">
-        <v>-7.383792158064312</v>
+        <v>-9.149847207841667</v>
       </c>
       <c r="F69">
-        <v>4.690571232288805</v>
+        <v>3.888356086764361</v>
       </c>
       <c r="G69">
-        <v>-6.438694412179022</v>
+        <v>-8.045759017671749</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.137360440579747</v>
       </c>
       <c r="E70">
-        <v>-5.830557272751433</v>
+        <v>-9.761915754718393</v>
       </c>
       <c r="F70">
-        <v>4.53256172569358</v>
+        <v>4.189424916113062</v>
       </c>
       <c r="G70">
-        <v>-6.669343430445585</v>
+        <v>-8.226571083390123</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.018297332491588</v>
       </c>
       <c r="E71">
-        <v>-6.748578580534383</v>
+        <v>-8.422845990650268</v>
       </c>
       <c r="F71">
-        <v>5.149999567240043</v>
+        <v>3.957649555388499</v>
       </c>
       <c r="G71">
-        <v>-6.690607064444325</v>
+        <v>-7.825577944400361</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.866329409120508</v>
       </c>
       <c r="E72">
-        <v>-5.928693832971657</v>
+        <v>-8.391219128180698</v>
       </c>
       <c r="F72">
-        <v>4.45368841998695</v>
+        <v>3.612194200347777</v>
       </c>
       <c r="G72">
-        <v>-5.712357410317385</v>
+        <v>-7.79828911752015</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.683221657458192</v>
       </c>
       <c r="E73">
-        <v>-6.974436221666942</v>
+        <v>-8.615138582437973</v>
       </c>
       <c r="F73">
-        <v>4.620424146176246</v>
+        <v>4.096519975995638</v>
       </c>
       <c r="G73">
-        <v>-5.797918459779849</v>
+        <v>-8.165551108010277</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.477584020290841</v>
       </c>
       <c r="E74">
-        <v>-6.807928760878911</v>
+        <v>-9.238143394043224</v>
       </c>
       <c r="F74">
-        <v>4.297623704255884</v>
+        <v>3.57993252714436</v>
       </c>
       <c r="G74">
-        <v>-5.873736573720238</v>
+        <v>-7.936302450506826</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.250828336987651</v>
       </c>
       <c r="E75">
-        <v>-6.656926795093143</v>
+        <v>-8.578439829079814</v>
       </c>
       <c r="F75">
-        <v>4.342073578184523</v>
+        <v>3.323240721252188</v>
       </c>
       <c r="G75">
-        <v>-5.807912996762909</v>
+        <v>-6.896383954074343</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.007802645965482</v>
       </c>
       <c r="E76">
-        <v>-6.607484915877397</v>
+        <v>-10.12179811258196</v>
       </c>
       <c r="F76">
-        <v>4.096586491644086</v>
+        <v>3.410734138256555</v>
       </c>
       <c r="G76">
-        <v>-4.86114000962336</v>
+        <v>-7.219993091083641</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.753174983119948</v>
       </c>
       <c r="E77">
-        <v>-8.490238740832417</v>
+        <v>-11.05996660122504</v>
       </c>
       <c r="F77">
-        <v>4.309895841394625</v>
+        <v>3.713297985989431</v>
       </c>
       <c r="G77">
-        <v>-5.1985441898948</v>
+        <v>-7.312701608365391</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.488951667231452</v>
       </c>
       <c r="E78">
-        <v>-7.902977174569711</v>
+        <v>-11.55156868254972</v>
       </c>
       <c r="F78">
-        <v>3.967584142596051</v>
+        <v>3.39035501053668</v>
       </c>
       <c r="G78">
-        <v>-5.242687004115442</v>
+        <v>-5.946068683207773</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.223382123293807</v>
       </c>
       <c r="E79">
-        <v>-7.688449775404343</v>
+        <v>-10.99126965052868</v>
       </c>
       <c r="F79">
-        <v>4.202818317039934</v>
+        <v>3.006971482527099</v>
       </c>
       <c r="G79">
-        <v>-6.041630890744376</v>
+        <v>-7.005790863056177</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.958785886513447</v>
       </c>
       <c r="E80">
-        <v>-8.639741781721646</v>
+        <v>-12.85503558396954</v>
       </c>
       <c r="F80">
-        <v>3.933293742114955</v>
+        <v>3.571808115798155</v>
       </c>
       <c r="G80">
-        <v>-4.824657797780591</v>
+        <v>-6.281436877972562</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.70673366469111</v>
       </c>
       <c r="E81">
-        <v>-10.00730017577203</v>
+        <v>-11.21129461713936</v>
       </c>
       <c r="F81">
-        <v>3.899964651124532</v>
+        <v>3.113253986512241</v>
       </c>
       <c r="G81">
-        <v>-4.733746906726665</v>
+        <v>-6.691706165563362</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.472946637862866</v>
       </c>
       <c r="E82">
-        <v>-9.020504933234585</v>
+        <v>-11.93095064949032</v>
       </c>
       <c r="F82">
-        <v>3.735724845457969</v>
+        <v>2.803134277856803</v>
       </c>
       <c r="G82">
-        <v>-5.290163537694131</v>
+        <v>-5.647815014483754</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.268457272780684</v>
       </c>
       <c r="E83">
-        <v>-10.87307195045448</v>
+        <v>-13.05508092325837</v>
       </c>
       <c r="F83">
-        <v>3.864020861667719</v>
+        <v>2.202038697651761</v>
       </c>
       <c r="G83">
-        <v>-3.37568829451576</v>
+        <v>-5.408843284731463</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.104854487673752</v>
       </c>
       <c r="E84">
-        <v>-11.99954797375851</v>
+        <v>-13.68747326148153</v>
       </c>
       <c r="F84">
-        <v>3.637460644522697</v>
+        <v>3.059628120509545</v>
       </c>
       <c r="G84">
-        <v>-3.235764776752924</v>
+        <v>-6.166087539747736</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.9887122772501</v>
       </c>
       <c r="E85">
-        <v>-12.50527436551311</v>
+        <v>-15.01303458758477</v>
       </c>
       <c r="F85">
-        <v>3.461217931723019</v>
+        <v>3.183196774561708</v>
       </c>
       <c r="G85">
-        <v>-3.009733969513645</v>
+        <v>-6.485426073011375</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.9352534649512</v>
       </c>
       <c r="E86">
-        <v>-13.52110618338773</v>
+        <v>-16.50922881429703</v>
       </c>
       <c r="F86">
-        <v>3.625804568985063</v>
+        <v>2.215888205882279</v>
       </c>
       <c r="G86">
-        <v>-2.356420981157251</v>
+        <v>-4.585540404024573</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.948105387771957</v>
       </c>
       <c r="E87">
-        <v>-15.13038093454553</v>
+        <v>-19.23881633563443</v>
       </c>
       <c r="F87">
-        <v>3.083214252708185</v>
+        <v>2.011834033501568</v>
       </c>
       <c r="G87">
-        <v>-2.736554372704065</v>
+        <v>-4.472372715310126</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.04072263814956</v>
       </c>
       <c r="E88">
-        <v>-15.59209055894558</v>
+        <v>-19.1271577520273</v>
       </c>
       <c r="F88">
-        <v>3.283559385834937</v>
+        <v>1.658917839893211</v>
       </c>
       <c r="G88">
-        <v>-2.957718678000615</v>
+        <v>-4.898866986588894</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.216330521177472</v>
       </c>
       <c r="E89">
-        <v>-17.65702036475517</v>
+        <v>-19.80354874370897</v>
       </c>
       <c r="F89">
-        <v>2.86490989450035</v>
+        <v>1.946312952368007</v>
       </c>
       <c r="G89">
-        <v>-2.636013104676399</v>
+        <v>-5.150296299205462</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.479461014662948</v>
       </c>
       <c r="E90">
-        <v>-18.23318716969909</v>
+        <v>-21.66273638992807</v>
       </c>
       <c r="F90">
-        <v>2.609915821349529</v>
+        <v>1.784455040398265</v>
       </c>
       <c r="G90">
-        <v>-3.078490689818768</v>
+        <v>-4.770480720030418</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.834708549839992</v>
       </c>
       <c r="E91">
-        <v>-20.38948799556144</v>
+        <v>-22.67713268154227</v>
       </c>
       <c r="F91">
-        <v>2.464393835897544</v>
+        <v>1.422225072301208</v>
       </c>
       <c r="G91">
-        <v>-2.728268077219269</v>
+        <v>-4.165104431082671</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.274267290237765</v>
       </c>
       <c r="E92">
-        <v>-23.00512552544382</v>
+        <v>-25.75500513880959</v>
       </c>
       <c r="F92">
-        <v>1.996410321591103</v>
+        <v>1.059659358550078</v>
       </c>
       <c r="G92">
-        <v>-2.536488174129289</v>
+        <v>-3.667529436530212</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.799958493625337</v>
       </c>
       <c r="E93">
-        <v>-24.85872956321147</v>
+        <v>-26.82664134188073</v>
       </c>
       <c r="F93">
-        <v>1.71556700048848</v>
+        <v>1.344384342851444</v>
       </c>
       <c r="G93">
-        <v>-2.609247343991391</v>
+        <v>-3.927357603179911</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.392996652941291</v>
       </c>
       <c r="E94">
-        <v>-26.59986894899862</v>
+        <v>-29.47720472754727</v>
       </c>
       <c r="F94">
-        <v>1.29088992443973</v>
+        <v>0.3810302878428667</v>
       </c>
       <c r="G94">
-        <v>-2.574989818751013</v>
+        <v>-3.164266924741284</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.044407596819131</v>
       </c>
       <c r="E95">
-        <v>-28.64238280847024</v>
+        <v>-31.5940489593808</v>
       </c>
       <c r="F95">
-        <v>1.295259369060427</v>
+        <v>0.2768089771066699</v>
       </c>
       <c r="G95">
-        <v>-2.430524232508297</v>
+        <v>-5.135822594107768</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.739493168355636</v>
       </c>
       <c r="E96">
-        <v>-30.76445289930862</v>
+        <v>-32.24759153545677</v>
       </c>
       <c r="F96">
-        <v>1.159467672752903</v>
+        <v>0.3830154632078701</v>
       </c>
       <c r="G96">
-        <v>-2.826624385191016</v>
+        <v>-3.983428312978547</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.450692250491573</v>
       </c>
       <c r="E97">
-        <v>-33.17939298964506</v>
+        <v>-35.60474630596214</v>
       </c>
       <c r="F97">
-        <v>0.7612970826108634</v>
+        <v>0.3897359192600374</v>
       </c>
       <c r="G97">
-        <v>-3.572298283547537</v>
+        <v>-5.061451188568041</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.181364768460472</v>
       </c>
       <c r="E98">
-        <v>-35.39115630091636</v>
+        <v>-36.75129252606817</v>
       </c>
       <c r="F98">
-        <v>0.8344737981396585</v>
+        <v>0.4263567429957015</v>
       </c>
       <c r="G98">
-        <v>-2.420258230791017</v>
+        <v>-5.291173254083608</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.889969682634783</v>
       </c>
       <c r="E99">
-        <v>-37.80802778541707</v>
+        <v>-39.6449715673105</v>
       </c>
       <c r="F99">
-        <v>0.05099389359486312</v>
+        <v>-0.2390856004066033</v>
       </c>
       <c r="G99">
-        <v>-2.760373747859121</v>
+        <v>-4.868499352357159</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.609628656701426</v>
       </c>
       <c r="E100">
-        <v>-40.48248566418508</v>
+        <v>-42.49262093450186</v>
       </c>
       <c r="F100">
-        <v>0.03275910368449332</v>
+        <v>0.08449323297119603</v>
       </c>
       <c r="G100">
-        <v>-2.015683081527764</v>
+        <v>-5.082824070569576</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.27922435967678</v>
       </c>
       <c r="E101">
-        <v>-43.03444832104562</v>
+        <v>-42.658598563831</v>
       </c>
       <c r="F101">
-        <v>0.0384192686262739</v>
+        <v>-0.4149300111685492</v>
       </c>
       <c r="G101">
-        <v>-3.309318477544451</v>
+        <v>-5.345181494011278</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.990714921314524</v>
       </c>
       <c r="E102">
-        <v>-44.34113496748489</v>
+        <v>-46.83098054638221</v>
       </c>
       <c r="F102">
-        <v>-0.4041996117384892</v>
+        <v>-1.287595522488359</v>
       </c>
       <c r="G102">
-        <v>-3.998908423920179</v>
+        <v>-6.123636414297662</v>
       </c>
     </row>
   </sheetData>
